--- a/Sprint-3/Ticket_Trade_Pricing_Toggle/Trade_Pricing_Toggle_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_Trade_Pricing_Toggle/Trade_Pricing_Toggle_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,9 +457,9 @@
         <v>User accesses mcstaging2.globewest.com without logging in.</v>
       </c>
       <c r="G2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com/indoor
-2. Inspect top utility header bar (.header__utility, .panel.header)
-3. Check DOM for .price-toggle or Trade/MSRP buttons.</v>
+        <v xml:space="preserve">Step 1: Navigate to https://mcstaging2.globewest.com/indoor
+Step 2: Inspect top utility header bar (.header__utility, .panel.header)
+Step 3: Check DOM for .price-toggle or Trade/MSRP buttons.</v>
       </c>
       <c r="H2" t="str">
         <v>Pricing toggle is completely hidden / not rendered in DOM. No trade discount or pricing toggle controls exposed to public guests.</v>
@@ -497,9 +497,9 @@
         <v>Guest browsing category PLP /indoor.</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect all 48 rendered category product cards
-2. Check for '$' dollar signs or wholesale pricing elements
-3. Verify presence of 'Add to Cart' CTAs.</v>
+        <v xml:space="preserve">Step 1: Inspect all 48 rendered category product cards
+Step 2: Check for '$' dollar signs or wholesale pricing elements
+Step 3: Verify presence of 'Add to Cart' CTAs.</v>
       </c>
       <c r="H3" t="str">
         <v>General public view: 'No pricing shown'. Add to cart buttons strictly suppressed.</v>
@@ -537,9 +537,9 @@
         <v>Guest navigates directly to a PDP via direct URL.</v>
       </c>
       <c r="G4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open PDP URL directly as logged-out guest
-2. Inspect pricing box and CTAs
-3. Verify Trade Pricing Toggle presence.</v>
+        <v xml:space="preserve">Step 1: Open PDP URL directly as logged-out guest
+Step 2: Inspect pricing box and CTAs
+Step 3: Verify Trade Pricing Toggle presence.</v>
       </c>
       <c r="H4" t="str">
         <v>No price displayed. Trade login prompt displayed. Toggle hidden.</v>
@@ -577,10 +577,10 @@
         <v>Trade customer logged in with US credentials.</v>
       </c>
       <c r="G5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as deepali.londhe@overdose.digital
-2. Navigate to https://mcstaging2.globewest.com/indoor
-3. Inspect top header utility bar for .price-toggle
-4. Check trigger button label and &lt;html&gt; class.</v>
+        <v xml:space="preserve">Step 1: Log in as trade.tester@globewest.com
+Step 2: Navigate to https://mcstaging2.globewest.com/indoor
+Step 3: Inspect top header utility bar for .price-toggle
+Step 4: Check trigger button label and &lt;html&gt; class.</v>
       </c>
       <c r="H5" t="str">
         <v>Logged-in trade customer: 'Trade pricing shown by default'. Toggle rendered in header utility bar showing 'Trade' with active class price-view-trade.</v>
@@ -618,9 +618,9 @@
         <v>User authenticated in Trade mode on category page.</v>
       </c>
       <c r="G6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. View product cards on /indoor in default Trade mode
-2. Inspect .price-box on category cards
-3. Check for wholesale price, MSRP line, and stock level.</v>
+        <v xml:space="preserve">Step 1: View product cards on /indoor in default Trade mode
+Step 2: Inspect .price-box on category cards
+Step 3: Check for wholesale price, MSRP line, and stock level.</v>
       </c>
       <c r="H6" t="str">
         <v>Trade customer sees wholesale discounted rate alongside MSRP (e.g., $638.00 • MSRP: $701.80).</v>
@@ -658,9 +658,9 @@
         <v>Trade customer views PDP.</v>
       </c>
       <c r="G7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to product PDP
-2. Inspect .price-box element
-3. Check for Trade price ($638.00) and MSRP ($701.80).</v>
+        <v xml:space="preserve">Step 1: Navigate to product PDP
+Step 2: Inspect .price-box element
+Step 3: Check for Trade price ($638.00) and MSRP ($701.80).</v>
       </c>
       <c r="H7" t="str">
         <v>PDP renders wholesale trade price prominently with secondary 'MSRP: $701.80' notation.</v>
@@ -698,9 +698,9 @@
         <v>Trade customer on any storefront page.</v>
       </c>
       <c r="G8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click .price-toggle__trigger button
-2. Verify dropdown / popover expansion
-3. Check options rendered.</v>
+        <v xml:space="preserve">Step 1: Click .price-toggle__trigger button
+Step 2: Verify dropdown / popover expansion
+Step 3: Check options rendered.</v>
       </c>
       <c r="H8" t="str">
         <v>Popover opens displaying selectable options: [ Trade ] and [ MSRP ].</v>
@@ -738,10 +738,10 @@
         <v>Trade user selects 'MSRP' from pricing toggle.</v>
       </c>
       <c r="G9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click toggle and select [ MSRP ]
-2. Verify &lt;html&gt; class updates to price-view-msrp
-3. Inspect product cards on PLP
-4. Confirm trade wholesale price is hidden.</v>
+        <v xml:space="preserve">Step 1: Click toggle and select [ MSRP ]
+Step 2: Verify &lt;html&gt; class updates to price-view-msrp
+Step 3: Inspect product cards on PLP
+Step 4: Confirm trade wholesale price is hidden.</v>
       </c>
       <c r="H9" t="str">
         <v>Toggle suppresses trade pricing to show RRP only, for showroom presentation scenarios where client is present.</v>
@@ -779,9 +779,9 @@
         <v>Trade user views PDP in MSRP mode.</v>
       </c>
       <c r="G10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. On PDP, switch toggle to MSRP
-2. Inspect PDP .price-box
-3. Verify wholesale price is hidden and MSRP alone is visible.</v>
+        <v xml:space="preserve">Step 1: On PDP, switch toggle to MSRP
+Step 2: Inspect PDP .price-box
+Step 3: Verify wholesale price is hidden and MSRP alone is visible.</v>
       </c>
       <c r="H10" t="str">
         <v>PDP suppresses wholesale trade price entirely; customer sees only '$701.80 MSRP'.</v>
@@ -819,9 +819,9 @@
         <v>Site is currently in MSRP mode.</v>
       </c>
       <c r="G11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click MSRP trigger button
-2. Select [ Trade ] option
-3. Inspect documentElement class and card pricing.</v>
+        <v xml:space="preserve">Step 1: Click MSRP trigger button
+Step 2: Select [ Trade ] option
+Step 3: Inspect documentElement class and card pricing.</v>
       </c>
       <c r="H11" t="str">
         <v>Root class switches back to price-view-trade; wholesale trade pricing restored.</v>
@@ -859,10 +859,10 @@
         <v>User adds product to cart while browsing in MSRP mode.</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Set toggle to MSRP mode
-2. Configure and add product to cart ($701.80 MSRP displayed on PDP)
-3. Navigate to /checkout/cart/
-4. Inspect line item price, subtotal, and grand total.</v>
+        <v xml:space="preserve">Step 1: Set toggle to MSRP mode
+Step 2: Configure and add product to cart ($701.80 MSRP displayed on PDP)
+Step 3: Navigate to /checkout/cart/
+Step 4: Inspect line item price, subtotal, and grand total.</v>
       </c>
       <c r="H12" t="str">
         <v>Cart and checkout always use trade pricing regardless of toggle state - the toggle affects display only, not transaction pricing.</v>
@@ -900,9 +900,9 @@
         <v>Viewport set to mobile dimension (390 x 844 px).</v>
       </c>
       <c r="G13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Emulate mobile viewport (iPhone 14/15/16)
-2. Navigate to /indoor
-3. Inspect header utility area for eye icon trigger button.</v>
+        <v xml:space="preserve">Step 1: Emulate mobile viewport (iPhone 14/15/16)
+Step 2: Navigate to /indoor
+Step 3: Inspect header utility area for eye icon trigger button.</v>
       </c>
       <c r="H13" t="str">
         <v>Mobile to utilise a slide-out triggered by an eye icon.</v>
@@ -940,9 +940,9 @@
         <v>Mobile viewport active on category page.</v>
       </c>
       <c r="G14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Tap mobile eye icon trigger
-2. Verify slide-out drawer / modal appearance
-3. Verify Trade and MSRP selection controls.</v>
+        <v xml:space="preserve">Step 1: Tap mobile eye icon trigger
+Step 2: Verify slide-out drawer / modal appearance
+Step 3: Verify Trade and MSRP selection controls.</v>
       </c>
       <c r="H14" t="str">
         <v>Slide-out drawer opens smoothly, allowing mobile trade user to switch between Trade and MSRP modes.</v>
@@ -980,9 +980,9 @@
         <v>User enters search query in header search input.</v>
       </c>
       <c r="G15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Execute catalog search (/catalogsearch/result/?q=chair)
-2. Inspect rendered SearchSpring product cards
-3. Toggle between Trade and MSRP modes.</v>
+        <v xml:space="preserve">Step 1: Execute catalog search (/catalogsearch/result/?q=chair)
+Step 2: Inspect rendered SearchSpring product cards
+Step 3: Toggle between Trade and MSRP modes.</v>
       </c>
       <c r="H15" t="str">
         <v>SearchSpring must be coordinated to respect the toggle state in search results.</v>
@@ -1020,9 +1020,9 @@
         <v>Salesperson logged in with internal tier credentials.</v>
       </c>
       <c r="G16" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Salesperson logs in
-2. Verify default tier display
-3. Toggle to MSRP mode for client presentation.</v>
+        <v xml:space="preserve">Step 1: Salesperson logs in
+Step 2: Verify default tier display
+Step 3: Toggle to MSRP mode for client presentation.</v>
       </c>
       <c r="H16" t="str">
         <v>Defaults to individual Salesperson's Tier view for internal reference. Ability to toggle to MSRP for customer-facing presentation.</v>
@@ -1060,9 +1060,9 @@
         <v>User creates quote from PDP or My Quotes.</v>
       </c>
       <c r="G17" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to quote presentation view
-2. Inspect quote line items and printed totals
-3. Verify RRP/MSRP presentation.</v>
+        <v xml:space="preserve">Step 1: Navigate to quote presentation view
+Step 2: Inspect quote line items and printed totals
+Step 3: Verify RRP/MSRP presentation.</v>
       </c>
       <c r="H17" t="str">
         <v>Quotes presented to end customers show RRP; trade margin is applied offline.</v>
@@ -1100,8 +1100,8 @@
         <v>Product pricing rendered across storefront.</v>
       </c>
       <c r="G18" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect displayed dollar amounts on PLP, PDP, and Cart
-2. Verify whether prices include or exclude state sales tax.</v>
+        <v xml:space="preserve">Step 1: Inspect displayed dollar amounts on PLP, PDP, and Cart
+Step 2: Verify whether prices include or exclude state sales tax.</v>
       </c>
       <c r="H18" t="str">
         <v>US tax display rules (whether RRP is shown inclusive or exclusive of tax) require a decision - flagged below.</v>
@@ -1119,9 +1119,173 @@
         <v>screenshots/02_TRADE_DEFAULT_PRICING_PLP.png</v>
       </c>
     </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-GW-TPT-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Accessibility &amp; Keyboard Navigation</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Trade Customer (Keyboard Only / WCAG)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Keyboard Focus &amp; Enter / Space Activation</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Verify Trade Pricing Toggle Keyboard Accessibility &amp; Tab Traversal</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Logged-in Trade Customer on mcstaging2.globewest.com/indoor.</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Navigate header using 'Tab' key
+Step 2: Focus on Trade Pricing Toggle button (.price-toggle)
+Step 3: Assert visible focus outline
+Step 4: Press 'Enter' or 'Space' to toggle between Trade and MSRP modes.</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Pricing toggle receives clean focus ring with minimum 3:1 contrast; Enter/Space switches pricing mode and updates DOM aria-checked/aria-expanded attributes.</v>
+      </c>
+      <c r="I19" t="str">
+        <v>PASS: Button is keyboard focusable; Enter and Space trigger toggle dropdown and switch pricing mode dynamically.</v>
+      </c>
+      <c r="J19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K19" t="str">
+        <v>P2 (Accessibility Compliance)</v>
+      </c>
+      <c r="L19" t="str">
+        <v>screenshots/01_GUEST_TOGGLE_HIDDEN.png</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-GW-TPT-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mobile Responsive Viewport</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Logged-in Trade Customer</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Mobile Drawer Toggle Placement &amp; State Synchronization</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Verify Trade Pricing Toggle Placement in Mobile Navigation Drawer</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Mobile viewport 390x844 (iPhone 14/15/17 Pro hardware profile).</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Open mobile hamburger menu drawer
+Step 2: Locate pricing toggle switch
+Step 3: Switch to 'MSRP' mode
+Step 4: Close menu and inspect PLP cards.</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Pricing toggle renders within mobile drawer or sticky header; switching to MSRP updates prices on mobile PLP immediately.</v>
+      </c>
+      <c r="I20" t="str">
+        <v>PASS: Mobile drawer provides responsive Trade/MSRP toggle; switching modes updates catalog prices reactively.</v>
+      </c>
+      <c r="J20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K20" t="str">
+        <v>P1 (Mobile Parity)</v>
+      </c>
+      <c r="L20" t="str">
+        <v>screenshots/03_MSRP_MODE_SWITCH_PLP.png</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-GW-TPT-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Catalog Search Results</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Logged-in Trade Customer</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Search Results Page Dual Pricing Toggle Integration</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Verify Trade vs MSRP Pricing Toggle Behavior on Search Results Page</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Logged in as Trade Customer on /catalogsearch/result?q=chair.</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Execute keyword search for 'chair'
+Step 2: Inspect rendered product cards under Trade mode
+Step 3: Toggle to MSRP mode via header utility bar
+Step 4: Verify instantaneous price updates on search grid.</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Search results cards display dual pricing (Trade + MSRP) in Trade mode and single MSRP in MSRP mode without page reload failure.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>PASS: Search result grid updates dynamically between Trade and MSRP modes aligned with PLP behavior.</v>
+      </c>
+      <c r="J21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K21" t="str">
+        <v>P1 (Catalog Search Integrity)</v>
+      </c>
+      <c r="L21" t="str">
+        <v>screenshots/02_TRADE_DEFAULT_PRICING_PLP.png</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-GW-TPT-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Session &amp; Page Refresh Persistence</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Logged-in Trade Customer</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Local Storage &amp; Session Cookie Persistence</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Verify Selected Pricing Toggle Mode Persists Across Browser Reloads and New Tabs</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Logged in as Trade Customer on mcstaging2.globewest.com.</v>
+      </c>
+      <c r="G22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Switch pricing toggle to 'MSRP'
+Step 2: Hard refresh page (Ctrl+F5)
+Step 3: Open a second product tab in the same browser session
+Step 4: Verify active pricing mode in both tabs.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>User's chosen mode (MSRP or Trade) is saved in session storage/cookie and persists across reloads and multi-tab browsing.</v>
+      </c>
+      <c r="I22" t="str">
+        <v>PASS: Mode preference persists in customer session; subsequent page loads retain chosen pricing mode without reverting.</v>
+      </c>
+      <c r="J22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K22" t="str">
+        <v>P2 (User Experience)</v>
+      </c>
+      <c r="L22" t="str">
+        <v>screenshots/03_MSRP_MODE_SWITCH_PLP.png</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L22"/>
   </ignoredErrors>
 </worksheet>
 </file>